--- a/DRIVE/1. Direção/0. Associativo/Folha de sócios e quotas.xlsx
+++ b/DRIVE/1. Direção/0. Associativo/Folha de sócios e quotas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36f760cd2ef29e19/M7Sound/0. Associativo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruisa\mind7\MINDSET\DRIVE\1. Direção\0. Associativo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7B9F09F-7BA3-48B0-9206-AA906ABAD38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63511FBC-D460-46FC-B68B-27DCBE973F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4128" yWindow="516" windowWidth="17280" windowHeight="8880" xr2:uid="{6531F716-14D6-4C5E-AAA6-16B677E61467}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6531F716-14D6-4C5E-AAA6-16B677E61467}"/>
   </bookViews>
   <sheets>
     <sheet name="Sócios" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
   <si>
     <t>Nº de Sócio</t>
   </si>
@@ -183,6 +183,36 @@
   </si>
   <si>
     <t>Orgãos internos</t>
+  </si>
+  <si>
+    <t>Inês César</t>
+  </si>
+  <si>
+    <t>Henrique Medeiros</t>
+  </si>
+  <si>
+    <t>João Aurélio</t>
+  </si>
+  <si>
+    <t>Diogo rouxinol</t>
+  </si>
+  <si>
+    <t>Rádio</t>
+  </si>
+  <si>
+    <t>Representante</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Eventos</t>
+  </si>
+  <si>
+    <t>Operações</t>
+  </si>
+  <si>
+    <t>Henrique</t>
   </si>
 </sst>
 </file>
@@ -204,7 +234,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,6 +244,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -316,17 +352,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -336,7 +369,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,7 +790,7 @@
       <c r="B8">
         <v>6</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
@@ -782,7 +823,7 @@
       <c r="B11">
         <v>9</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
@@ -793,7 +834,7 @@
       <c r="B12">
         <v>10</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
@@ -804,7 +845,7 @@
       <c r="B13">
         <v>11</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -812,7 +853,7 @@
       <c r="B14">
         <v>12</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -820,7 +861,7 @@
       <c r="B15">
         <v>13</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -851,21 +892,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E15220F-1A27-4385-9DBC-9509A8FC76C7}">
-  <dimension ref="B2:E15"/>
+  <dimension ref="B2:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="21.21875" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
@@ -879,105 +920,178 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="9"/>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="10"/>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="9"/>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="10"/>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="9"/>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>5</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="10"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>3</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>40</v>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="13"/>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="13"/>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B12"/>
@@ -998,18 +1112,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
